--- a/amostras/principal/P04/matriz_rastreabilidade_P04.xlsx
+++ b/amostras/principal/P04/matriz_rastreabilidade_P04.xlsx
@@ -514,6 +514,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -691,6 +692,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -748,6 +750,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -805,6 +808,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1102,6 +1106,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1159,6 +1164,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1216,6 +1222,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1273,6 +1280,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1450,6 +1458,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1507,6 +1516,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1564,6 +1574,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Nenhum</t>
